--- a/CardsRPG2GameClient/lubanConfig/MiniTemplate/Datas/#HeroDataCfg.xlsx
+++ b/CardsRPG2GameClient/lubanConfig/MiniTemplate/Datas/#HeroDataCfg.xlsx
@@ -629,7 +629,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>zuoluouooer</t>
+    <t>zuoluo</t>
   </si>
   <si>
     <t>左罗</t>
